--- a/src/Verify.OpenXml.Tests/ExcelBannerTests.MergedBannerRowIsSkipped.verified.xlsx
+++ b/src/Verify.OpenXml.Tests/ExcelBannerTests.MergedBannerRowIsSkipped.verified.xlsx
@@ -63,6 +63,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
+  <pageSetup paperSize="9"/>
 </worksheet>
 </file>
 
